--- a/sports_forms/012_youth_athlete_confidence_survey--sports_forms.xlsx
+++ b/sports_forms/012_youth_athlete_confidence_survey--sports_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,20 +525,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>athlete_name</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is your name?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>This is the athlete's name</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -548,43 +552,51 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>age_group</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What is your age group?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please select the age group of the athlete</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>event_competed</t>
+          <t>events_competed</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>events_competed</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Which events have you competed in?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please select the events that the athlete has competed in</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,13 +606,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sports_competed</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Which sports have you competed in?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please select the sports that the athlete has competed in</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +628,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>confidence_level_road</t>
+          <t>gender</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>confidence_level_road</t>
+          <t>What is your gender?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,15 +651,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>confidence_level_race</t>
+          <t>sports_competed_other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>confidence_level_race</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Have you competed in any other sports?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please enter other sports</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -658,15 +678,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>confidence_level_sprint</t>
+          <t>events_competed_other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>confidence_level_sprint</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Have you competed in any other events?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please enter other events</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -681,18 +705,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>confidence_level_jumps</t>
+          <t>overall_confidence</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>confidence_level_jumps</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>What is your overall confidence level in competitions?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>On a scale of 1-10</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,18 +732,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>confidence_level_distance</t>
+          <t>event_confidence</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>confidence_level_distance</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>How confident are you in your performance in events?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>On a scale of 1-10</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,18 +759,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>confidence_level_throws</t>
+          <t>competition_confidence</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>confidence_level_throws</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Competition Confidence</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>On a scale of 1-10</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,18 +786,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>event_confidence</t>
+          <t>overall_confidence_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>event_confidence</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>How confident are you in your overall performance?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>On a scale of 1-10</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,18 +813,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>event_performance</t>
+          <t>training_confidence</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>event_performance</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>How confident are you in your training?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>On a scale of 1-10</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,18 +840,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>training_confidence</t>
+          <t>performance_event</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>training_confidence</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Performance Event</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>On a scale of 1-10</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -824,13 +872,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>training_performance</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Training Performance</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>On a scale of 1-10</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -842,18 +894,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>competition_confidence</t>
+          <t>competition_training_confidence</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>competition_confidence</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>How confident are you in your performance in competitions?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>On a scale of 1-10</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -865,18 +921,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>competition_performance</t>
+          <t>performance_competition</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>competition_performance</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Performance Competition</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>On a scale of 1-10</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -888,18 +948,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>overall_confidence</t>
+          <t>overall_training_confidence</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>overall_confidence</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>How confident are you in your overall training?</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>On a scale of 1-10</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -911,452 +975,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>overall_performance</t>
+          <t>performance_training</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>overall_performance</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>How confident are you in your performance in training?</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>On a scale of 1-10</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>athlete_name_hint</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>athlete_name</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>This is the athlete's name</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>event_type</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>event_type</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>athlete_gender</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>gender</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>age_group</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>age_group</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Please select the age group of the athlete</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>events_competed</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>events_competed</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Please select the events that the athlete has competed in</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>sports_competed</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>sports_competed</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>sports_competed_other</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>sports_competed_other</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Please enter other sports</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>sports_competed_other</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>sports_competed_other</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>events_competed_other</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>events_competed_other</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Please enter other events</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>sports_competed</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>sports_competed</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>events_competed</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>events_competed</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>athlete_gender</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>gender</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>athlete_name</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>athlete_name</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>sports_competed_other</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>sports_competed_other</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>events_competed_other</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>events_competed_other</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>age_group</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>age_group</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>sports_competed</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>sports_competed</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>events_competed</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>events_competed</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1399,330 +1033,330 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>event_type_choices</t>
+          <t>age_group_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>u11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Running</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>event_type_choices</t>
+          <t>age_group_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>swimming</t>
+          <t>u12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Swimming</t>
+          <t>U12</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>event_type_choices</t>
+          <t>age_group_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>cycling</t>
+          <t>u13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cycling</t>
+          <t>U13</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>event_type_choices</t>
+          <t>age_group_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>u14</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Basketball</t>
+          <t>U14</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>event_type_choices</t>
+          <t>age_group_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>soccer</t>
+          <t>u15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Soccer</t>
+          <t>U15</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>event_type_choices</t>
+          <t>age_group_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>u16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tennis</t>
+          <t>U16</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>event_type_choices</t>
+          <t>age_group_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>volleyball</t>
+          <t>u17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Volleyball</t>
+          <t>U17</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>event_type_choices</t>
+          <t>age_group_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>baseball</t>
+          <t>u18</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Baseball</t>
+          <t>U18</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>event_type_choices</t>
+          <t>events_competed_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>softball</t>
+          <t>running</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Softball</t>
+          <t>Running</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>event_type_choices</t>
+          <t>events_competed_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>golf</t>
+          <t>swimming</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Golf</t>
+          <t>Swimming</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>event_type_choices</t>
+          <t>events_competed_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>cycling</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Cycling</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>age_group_choices</t>
+          <t>events_competed_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>u11</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>Basketball</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>age_group_choices</t>
+          <t>events_competed_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>u12</t>
+          <t>soccer</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>Soccer</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>age_group_choices</t>
+          <t>events_competed_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>u13</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>U13</t>
+          <t>Tennis</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>age_group_choices</t>
+          <t>events_competed_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>u14</t>
+          <t>volleyball</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>U14</t>
+          <t>Volleyball</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>age_group_choices</t>
+          <t>events_competed_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>u15</t>
+          <t>baseball</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>U15</t>
+          <t>Baseball</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>age_group_choices</t>
+          <t>events_competed_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>u16</t>
+          <t>softball</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>Softball</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>age_group_choices</t>
+          <t>events_competed_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>u17</t>
+          <t>golf</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>U17</t>
+          <t>Golf</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>age_group_choices</t>
+          <t>events_competed_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>u18</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>U18</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>events_competed_choices</t>
+          <t>sports_competed_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1739,7 +1373,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>events_competed_choices</t>
+          <t>sports_competed_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1756,7 +1390,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>events_competed_choices</t>
+          <t>sports_competed_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1773,7 +1407,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>events_competed_choices</t>
+          <t>sports_competed_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1790,7 +1424,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>events_competed_choices</t>
+          <t>sports_competed_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1807,7 +1441,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>events_competed_choices</t>
+          <t>sports_competed_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1824,7 +1458,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>events_competed_choices</t>
+          <t>sports_competed_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1841,7 +1475,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>events_competed_choices</t>
+          <t>sports_competed_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1858,7 +1492,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>events_competed_choices</t>
+          <t>sports_competed_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1875,7 +1509,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>events_competed_choices</t>
+          <t>sports_competed_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1892,7 +1526,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>events_competed_choices</t>
+          <t>sports_competed_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1903,329 +1537,6 @@
       <c r="C31" t="inlineStr">
         <is>
           <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>sports_competed_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Running</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>sports_competed_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>swimming</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Swimming</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>sports_competed_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>cycling</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Cycling</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>sports_competed_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>basketball</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Basketball</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>sports_competed_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>soccer</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Soccer</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>sports_competed_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>tennis</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Tennis</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>sports_competed_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>volleyball</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Volleyball</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>sports_competed_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>baseball</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Baseball</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>sports_competed_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>softball</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Softball</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>sports_competed_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>golf</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Golf</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>sports_competed_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>sports_competed_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>sports_competed_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>events_competed_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>events_competed_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>sports_competed_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>sports_competed_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>events_competed_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>events_competed_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>
